--- a/data_files/protein/PBDB_Proteins_Master_With_2025_2026.xlsx
+++ b/data_files/protein/PBDB_Proteins_Master_With_2025_2026.xlsx
@@ -2568,7 +2568,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Peroxidase</t>
+          <t>Oxidoreductase</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
